--- a/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.13</v>
+        <v>0.9535</v>
       </c>
       <c r="E2">
-        <v>0.196</v>
+        <v>0.0452</v>
       </c>
       <c r="F2">
-        <v>0.0617</v>
+        <v>-0.0408</v>
       </c>
       <c r="G2">
-        <v>0.116203561190023</v>
+        <v>0.1557362438469238</v>
       </c>
       <c r="H2">
-        <v>0.116203561190023</v>
+        <v>0.1557362438469238</v>
       </c>
       <c r="I2">
-        <v>0.1197530243729805</v>
+        <v>0.06749758904535337</v>
       </c>
       <c r="J2">
-        <v>0.1075264145819727</v>
+        <v>0.06320521855172506</v>
       </c>
       <c r="K2">
-        <v>8083</v>
+        <v>4243.7</v>
       </c>
       <c r="L2">
-        <v>0.08463218556886692</v>
+        <v>0.06465319579084645</v>
       </c>
       <c r="M2">
-        <v>2348.8</v>
+        <v>3867.2</v>
       </c>
       <c r="N2">
-        <v>0.01846175128826679</v>
+        <v>0.02847977282167149</v>
       </c>
       <c r="O2">
-        <v>0.2905851787702586</v>
+        <v>0.9112802507246035</v>
       </c>
       <c r="P2">
-        <v>2241.8</v>
+        <v>2422.2</v>
       </c>
       <c r="Q2">
-        <v>0.01762072293853734</v>
+        <v>0.01783815311560113</v>
       </c>
       <c r="R2">
-        <v>0.2773475194853396</v>
+        <v>0.5707755025096024</v>
       </c>
       <c r="S2">
-        <v>107</v>
+        <v>1445</v>
       </c>
       <c r="T2">
-        <v>0.04555517711171662</v>
+        <v>0.3736553578816715</v>
       </c>
       <c r="U2">
-        <v>13108.8</v>
+        <v>12399.3</v>
       </c>
       <c r="V2">
-        <v>0.1030361909433037</v>
+        <v>0.09131393440932752</v>
       </c>
       <c r="W2">
-        <v>0.1117145763180503</v>
+        <v>0.05504874151356561</v>
       </c>
       <c r="X2">
-        <v>0.08776269814656666</v>
+        <v>0.1328818500431708</v>
       </c>
       <c r="Y2">
-        <v>0.02395187817148363</v>
+        <v>-0.07783310852960518</v>
       </c>
       <c r="Z2">
-        <v>1.224656385479137</v>
+        <v>0.7479037174191709</v>
       </c>
       <c r="AA2">
-        <v>0.1206298748769481</v>
+        <v>0.04185052849586253</v>
       </c>
       <c r="AB2">
-        <v>0.06141010360921065</v>
+        <v>0.09639699992194666</v>
       </c>
       <c r="AC2">
-        <v>0.05921977126773749</v>
+        <v>-0.05723036299507735</v>
       </c>
       <c r="AD2">
-        <v>30021</v>
+        <v>31734.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>30021</v>
+        <v>31734.4</v>
       </c>
       <c r="AG2">
-        <v>16912.2</v>
+        <v>19335.1</v>
       </c>
       <c r="AH2">
-        <v>0.1909171731971901</v>
+        <v>0.1894342235646661</v>
       </c>
       <c r="AI2">
-        <v>0.2802089643347499</v>
+        <v>0.3567771514400646</v>
       </c>
       <c r="AJ2">
-        <v>0.1173338772587822</v>
+        <v>0.1246439109169709</v>
       </c>
       <c r="AK2">
-        <v>0.1798613407976893</v>
+        <v>0.2525875887187272</v>
       </c>
       <c r="AL2">
-        <v>602</v>
+        <v>796.6999999999999</v>
       </c>
       <c r="AM2">
-        <v>602</v>
+        <v>796.6999999999999</v>
       </c>
       <c r="AN2">
-        <v>2.534786720253977</v>
+        <v>6.475086716996531</v>
       </c>
       <c r="AO2">
-        <v>18.99883720930232</v>
+        <v>5.560938872850508</v>
       </c>
       <c r="AP2">
-        <v>1.427961092910939</v>
+        <v>3.945133646194654</v>
       </c>
       <c r="AQ2">
-        <v>18.99883720930232</v>
+        <v>5.560938872850508</v>
       </c>
     </row>
     <row r="3">
@@ -725,118 +725,118 @@
         </is>
       </c>
       <c r="F3">
-        <v>0.0617</v>
+        <v>-0.0408</v>
       </c>
       <c r="G3">
-        <v>0.154770767135724</v>
+        <v>0.3241958485184598</v>
       </c>
       <c r="H3">
-        <v>0.154770767135724</v>
+        <v>0.3241958485184598</v>
       </c>
       <c r="I3">
-        <v>0.1677712210621879</v>
+        <v>0.1388448740294723</v>
       </c>
       <c r="J3">
-        <v>0.1369499919847705</v>
+        <v>0.1258217071850206</v>
       </c>
       <c r="K3">
-        <v>6827</v>
+        <v>3611</v>
       </c>
       <c r="L3">
-        <v>0.12395823876532</v>
+        <v>0.1430438916178102</v>
       </c>
       <c r="M3">
-        <v>2210</v>
+        <v>3684</v>
       </c>
       <c r="N3">
-        <v>0.01817078565215032</v>
+        <v>0.02817127585138964</v>
       </c>
       <c r="O3">
-        <v>0.3237146623700015</v>
+        <v>1.020216006646358</v>
       </c>
       <c r="P3">
-        <v>2103</v>
+        <v>2239</v>
       </c>
       <c r="Q3">
-        <v>0.01729102363188784</v>
+        <v>0.01712146759806227</v>
       </c>
       <c r="R3">
-        <v>0.3080415995312729</v>
+        <v>0.6200498476876212</v>
       </c>
       <c r="S3">
-        <v>107</v>
+        <v>1445</v>
       </c>
       <c r="T3">
-        <v>0.04841628959276018</v>
+        <v>0.3922366992399566</v>
       </c>
       <c r="U3">
-        <v>6176</v>
+        <v>5576</v>
       </c>
       <c r="V3">
-        <v>0.0507795349265522</v>
+        <v>0.04263926008342796</v>
       </c>
       <c r="W3">
-        <v>0.1201851982254771</v>
+        <v>0.06126153637350706</v>
       </c>
       <c r="X3">
-        <v>0.06515718786442265</v>
+        <v>0.0993054883224043</v>
       </c>
       <c r="Y3">
-        <v>0.05502801036105442</v>
+        <v>-0.03804395194889724</v>
       </c>
       <c r="Z3">
-        <v>0.9229931288754818</v>
+        <v>0.3911615222511466</v>
       </c>
       <c r="AA3">
-        <v>0.1264039016014955</v>
+        <v>0.0492166105147307</v>
       </c>
       <c r="AB3">
-        <v>0.06122912414752425</v>
+        <v>0.09464332599678446</v>
       </c>
       <c r="AC3">
-        <v>0.06517477745397124</v>
+        <v>-0.04542671548205376</v>
       </c>
       <c r="AD3">
-        <v>13375</v>
+        <v>13297</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13375</v>
+        <v>13297</v>
       </c>
       <c r="AG3">
-        <v>7199</v>
+        <v>7721</v>
       </c>
       <c r="AH3">
-        <v>0.09907495474033844</v>
+        <v>0.09229637290594404</v>
       </c>
       <c r="AI3">
-        <v>0.1837427189801077</v>
+        <v>0.2429341372065406</v>
       </c>
       <c r="AJ3">
-        <v>0.05588296481678709</v>
+        <v>0.05575031138870336</v>
       </c>
       <c r="AK3">
-        <v>0.1080671310195749</v>
+        <v>0.1570617791248805</v>
       </c>
       <c r="AL3">
-        <v>325</v>
+        <v>364</v>
       </c>
       <c r="AM3">
-        <v>325</v>
+        <v>364</v>
       </c>
       <c r="AN3">
-        <v>1.426818860678472</v>
+        <v>3.653021978021978</v>
       </c>
       <c r="AO3">
-        <v>28.43076923076923</v>
+        <v>9.62912087912088</v>
       </c>
       <c r="AP3">
-        <v>0.7679752506934073</v>
+        <v>2.121153846153846</v>
       </c>
       <c r="AQ3">
-        <v>28.43076923076923</v>
+        <v>9.62912087912088</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yunfeng Financial Group Limited (SEHK:376)</t>
+          <t>China Taiping Insurance Holdings Company Limited (SEHK:966)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,113 +855,122 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.107</v>
+      </c>
+      <c r="E4">
+        <v>0.0452</v>
+      </c>
       <c r="G4">
-        <v>0.09027099609375</v>
+        <v>0.04822702986417039</v>
       </c>
       <c r="H4">
-        <v>0.09027099609375</v>
+        <v>0.04822702986417039</v>
       </c>
       <c r="I4">
-        <v>0.11614990234375</v>
+        <v>0.02285993828937747</v>
       </c>
       <c r="J4">
-        <v>0.1158294184304289</v>
+        <v>0.02285993828937747</v>
       </c>
       <c r="K4">
-        <v>124.7</v>
+        <v>651.1</v>
       </c>
       <c r="L4">
-        <v>0.07611083984375</v>
+        <v>0.01658950715583334</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>183.2</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.04089011896524786</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.2813699892489633</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>183.2</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.04089011896524786</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2813699892489633</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>459.5</v>
+        <v>6426.1</v>
       </c>
       <c r="V4">
-        <v>0.6861281170673436</v>
+        <v>1.434301274468228</v>
       </c>
       <c r="W4">
-        <v>0.09446254071661239</v>
+        <v>0.05504874151356561</v>
       </c>
       <c r="X4">
-        <v>0.08776269814656666</v>
+        <v>0.2816271256088478</v>
       </c>
       <c r="Y4">
-        <v>0.00669984257004573</v>
+        <v>-0.2265783840952822</v>
       </c>
       <c r="Z4">
-        <v>1.041444190185609</v>
+        <v>1.830736722299447</v>
       </c>
       <c r="AA4">
-        <v>0.1206298748769481</v>
+        <v>0.04185052849586253</v>
       </c>
       <c r="AB4">
-        <v>0.06141010360921065</v>
+        <v>0.09908089149093988</v>
       </c>
       <c r="AC4">
-        <v>0.05921977126773749</v>
+        <v>-0.05723036299507735</v>
       </c>
       <c r="AD4">
-        <v>469.1</v>
+        <v>17996.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>469.1</v>
+        <v>17996.6</v>
       </c>
       <c r="AG4">
-        <v>9.600000000000023</v>
+        <v>11570.5</v>
       </c>
       <c r="AH4">
-        <v>0.4119248331577098</v>
+        <v>0.8006709110242071</v>
       </c>
       <c r="AI4">
-        <v>0.1544819864321939</v>
+        <v>0.5661141816374486</v>
       </c>
       <c r="AJ4">
-        <v>0.01413219490652145</v>
+        <v>0.7208674957011487</v>
       </c>
       <c r="AK4">
-        <v>0.003725117380000785</v>
+        <v>0.4561852418426406</v>
       </c>
       <c r="AL4">
-        <v>20.6</v>
+        <v>414.4</v>
       </c>
       <c r="AM4">
-        <v>20.6</v>
+        <v>414.4</v>
       </c>
       <c r="AN4">
-        <v>2.405641025641026</v>
+        <v>14.91266158435532</v>
       </c>
       <c r="AO4">
-        <v>9.237864077669903</v>
+        <v>2.165057915057915</v>
       </c>
       <c r="AP4">
-        <v>0.04923076923076935</v>
+        <v>9.587752734504473</v>
       </c>
       <c r="AQ4">
-        <v>9.237864077669903</v>
+        <v>2.165057915057915</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>China Taiping Insurance Holdings Company Limited (SEHK:966)</t>
+          <t>Yunfeng Financial Group Limited (SEHK:376)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,121 +990,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.13</v>
-      </c>
-      <c r="E5">
-        <v>0.196</v>
+        <v>1.8</v>
       </c>
       <c r="G5">
-        <v>0.06254575449811826</v>
+        <v>0.1268539521898447</v>
       </c>
       <c r="H5">
-        <v>0.06254575449811826</v>
+        <v>0.1268539521898447</v>
       </c>
       <c r="I5">
-        <v>0.05173480435118833</v>
+        <v>0.0246030361193509</v>
       </c>
       <c r="J5">
-        <v>0.04553560148047563</v>
+        <v>0.02221697684117867</v>
       </c>
       <c r="K5">
-        <v>1131.3</v>
+        <v>-18.4</v>
       </c>
       <c r="L5">
-        <v>0.02916172604010929</v>
+        <v>-0.01605304484383179</v>
       </c>
       <c r="M5">
-        <v>138.8</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.02814445323113734</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.1226907098028817</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>138.8</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.02814445323113734</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.1226907098028817</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>6473.3</v>
+        <v>397.2</v>
       </c>
       <c r="V5">
-        <v>1.312589979114707</v>
+        <v>0.7413213885778276</v>
       </c>
       <c r="W5">
-        <v>0.1117145763180503</v>
+        <v>-0.0103446337212571</v>
       </c>
       <c r="X5">
-        <v>0.1865208940174648</v>
+        <v>0.1328818500431708</v>
       </c>
       <c r="Y5">
-        <v>-0.07480631769941448</v>
+        <v>-0.1432264837644279</v>
       </c>
       <c r="Z5">
-        <v>2.316903469323156</v>
+        <v>0.6409439132136666</v>
       </c>
       <c r="AA5">
-        <v>0.1055015930478306</v>
+        <v>0.01423983607636247</v>
       </c>
       <c r="AB5">
-        <v>0.06549035972602853</v>
+        <v>0.09639699992194666</v>
       </c>
       <c r="AC5">
-        <v>0.04001123332180209</v>
+        <v>-0.08215716384558419</v>
       </c>
       <c r="AD5">
-        <v>16176.9</v>
+        <v>440.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>16176.9</v>
+        <v>440.8</v>
       </c>
       <c r="AG5">
-        <v>9703.599999999999</v>
+        <v>43.60000000000002</v>
       </c>
       <c r="AH5">
-        <v>0.7663653676700493</v>
+        <v>0.4513618677042802</v>
       </c>
       <c r="AI5">
-        <v>0.5166803473728253</v>
+        <v>0.1819457629917035</v>
       </c>
       <c r="AJ5">
-        <v>0.6630270646997328</v>
+        <v>0.07525025888850539</v>
       </c>
       <c r="AK5">
-        <v>0.3907070381703978</v>
+        <v>0.02152554924709949</v>
       </c>
       <c r="AL5">
-        <v>256.4</v>
+        <v>18.3</v>
       </c>
       <c r="AM5">
-        <v>256.4</v>
+        <v>18.3</v>
       </c>
       <c r="AN5">
-        <v>7.111975731996835</v>
+        <v>8.132841328413283</v>
       </c>
       <c r="AO5">
-        <v>7.827613104524182</v>
+        <v>1.540983606557377</v>
       </c>
       <c r="AP5">
-        <v>4.266068759342302</v>
+        <v>0.8044280442804432</v>
       </c>
       <c r="AQ5">
-        <v>7.827613104524182</v>
+        <v>1.540983606557377</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.9535</v>
+        <v>0.7048500000000001</v>
       </c>
       <c r="E2">
-        <v>0.0452</v>
+        <v>-0.163</v>
       </c>
       <c r="F2">
-        <v>-0.0408</v>
+        <v>2.082</v>
       </c>
       <c r="G2">
-        <v>0.1557362438469238</v>
+        <v>0.03246081980099513</v>
       </c>
       <c r="H2">
-        <v>0.1557362438469238</v>
+        <v>0.03246081980099513</v>
       </c>
       <c r="I2">
-        <v>0.06749758904535337</v>
+        <v>0.4041860079488603</v>
       </c>
       <c r="J2">
-        <v>0.06320521855172506</v>
+        <v>0.3631624815321022</v>
       </c>
       <c r="K2">
-        <v>4243.7</v>
+        <v>1505.6</v>
       </c>
       <c r="L2">
-        <v>0.06465319579084645</v>
+        <v>0.01580116724616174</v>
       </c>
       <c r="M2">
-        <v>3867.2</v>
+        <v>6800</v>
       </c>
       <c r="N2">
-        <v>0.02847977282167149</v>
+        <v>0.0665063992848606</v>
       </c>
       <c r="O2">
-        <v>0.9112802507246035</v>
+        <v>4.516471838469713</v>
       </c>
       <c r="P2">
-        <v>2422.2</v>
+        <v>2492</v>
       </c>
       <c r="Q2">
-        <v>0.01783815311560113</v>
+        <v>0.02437263926733421</v>
       </c>
       <c r="R2">
-        <v>0.5707755025096024</v>
+        <v>1.655154091392136</v>
       </c>
       <c r="S2">
-        <v>1445</v>
+        <v>4308</v>
       </c>
       <c r="T2">
-        <v>0.3736553578816715</v>
+        <v>0.6335294117647059</v>
       </c>
       <c r="U2">
-        <v>12399.3</v>
+        <v>14293.5</v>
       </c>
       <c r="V2">
-        <v>0.09131393440932752</v>
+        <v>0.1397954732614934</v>
       </c>
       <c r="W2">
-        <v>0.05504874151356561</v>
+        <v>0.03449301219149568</v>
       </c>
       <c r="X2">
-        <v>0.1328818500431708</v>
+        <v>0.1125797186908479</v>
       </c>
       <c r="Y2">
-        <v>-0.07783310852960518</v>
+        <v>-0.07808670649935218</v>
       </c>
       <c r="Z2">
-        <v>0.7479037174191709</v>
+        <v>1.351419084994759</v>
       </c>
       <c r="AA2">
-        <v>0.04185052849586253</v>
+        <v>0.07592477205669876</v>
       </c>
       <c r="AB2">
-        <v>0.09639699992194666</v>
+        <v>0.08240411114023963</v>
       </c>
       <c r="AC2">
-        <v>-0.05723036299507735</v>
+        <v>-0.006479339083540869</v>
       </c>
       <c r="AD2">
-        <v>31734.4</v>
+        <v>30959.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>31734.4</v>
+        <v>30959.5</v>
       </c>
       <c r="AG2">
-        <v>19335.1</v>
+        <v>16666</v>
       </c>
       <c r="AH2">
-        <v>0.1894342235646661</v>
+        <v>0.2324194307583858</v>
       </c>
       <c r="AI2">
-        <v>0.3567771514400646</v>
+        <v>0.3397099471005134</v>
       </c>
       <c r="AJ2">
-        <v>0.1246439109169709</v>
+        <v>0.1401542992369134</v>
       </c>
       <c r="AK2">
-        <v>0.2525875887187272</v>
+        <v>0.2168877274809478</v>
       </c>
       <c r="AL2">
-        <v>796.6999999999999</v>
+        <v>7270.6</v>
       </c>
       <c r="AM2">
-        <v>796.6999999999999</v>
+        <v>7270.6</v>
       </c>
       <c r="AN2">
-        <v>6.475086716996531</v>
+        <v>0.7937315728752724</v>
       </c>
       <c r="AO2">
-        <v>5.560938872850508</v>
+        <v>5.297018127802382</v>
       </c>
       <c r="AP2">
-        <v>3.945133646194654</v>
+        <v>0.4272785540315344</v>
       </c>
       <c r="AQ2">
-        <v>5.560938872850508</v>
+        <v>5.297018127802382</v>
       </c>
     </row>
     <row r="3">
@@ -725,118 +725,118 @@
         </is>
       </c>
       <c r="F3">
-        <v>-0.0408</v>
+        <v>2.082</v>
       </c>
       <c r="G3">
-        <v>0.3241958485184598</v>
+        <v>0.03689572009646881</v>
       </c>
       <c r="H3">
-        <v>0.3241958485184598</v>
+        <v>0.03689572009646881</v>
       </c>
       <c r="I3">
-        <v>0.1388448740294723</v>
+        <v>0.6757316151326446</v>
       </c>
       <c r="J3">
-        <v>0.1258217071850206</v>
+        <v>0.5277386834534038</v>
       </c>
       <c r="K3">
-        <v>3611</v>
+        <v>989</v>
       </c>
       <c r="L3">
-        <v>0.1430438916178102</v>
+        <v>0.01779993520751593</v>
       </c>
       <c r="M3">
-        <v>3684</v>
+        <v>6589</v>
       </c>
       <c r="N3">
-        <v>0.02817127585138964</v>
+        <v>0.06678559482662504</v>
       </c>
       <c r="O3">
-        <v>1.020216006646358</v>
+        <v>6.662285136501517</v>
       </c>
       <c r="P3">
-        <v>2239</v>
+        <v>2281</v>
       </c>
       <c r="Q3">
-        <v>0.01712146759806227</v>
+        <v>0.02312003973281708</v>
       </c>
       <c r="R3">
-        <v>0.6200498476876212</v>
+        <v>2.306370070778564</v>
       </c>
       <c r="S3">
-        <v>1445</v>
+        <v>4308</v>
       </c>
       <c r="T3">
-        <v>0.3922366992399566</v>
+        <v>0.653816967673395</v>
       </c>
       <c r="U3">
-        <v>5576</v>
+        <v>6666</v>
       </c>
       <c r="V3">
-        <v>0.04263926008342796</v>
+        <v>0.06756606087635188</v>
       </c>
       <c r="W3">
-        <v>0.06126153637350706</v>
+        <v>0.0241219512195122</v>
       </c>
       <c r="X3">
-        <v>0.0993054883224043</v>
+        <v>0.08623485124113092</v>
       </c>
       <c r="Y3">
-        <v>-0.03804395194889724</v>
+        <v>-0.06211290002161873</v>
       </c>
       <c r="Z3">
-        <v>0.3911615222511466</v>
+        <v>1.18272382817489</v>
       </c>
       <c r="AA3">
-        <v>0.0492166105147307</v>
+        <v>0.6241691159699865</v>
       </c>
       <c r="AB3">
-        <v>0.09464332599678446</v>
+        <v>0.08139928650075584</v>
       </c>
       <c r="AC3">
-        <v>-0.04542671548205376</v>
+        <v>0.5427698294692307</v>
       </c>
       <c r="AD3">
-        <v>13297</v>
+        <v>13310</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13297</v>
+        <v>13310</v>
       </c>
       <c r="AG3">
-        <v>7721</v>
+        <v>6644</v>
       </c>
       <c r="AH3">
-        <v>0.09229637290594404</v>
+        <v>0.1188721878377051</v>
       </c>
       <c r="AI3">
-        <v>0.2429341372065406</v>
+        <v>0.2394487820674271</v>
       </c>
       <c r="AJ3">
-        <v>0.05575031138870336</v>
+        <v>0.06309411887600543</v>
       </c>
       <c r="AK3">
-        <v>0.1570617791248805</v>
+        <v>0.1358135731807032</v>
       </c>
       <c r="AL3">
-        <v>364</v>
+        <v>6756</v>
       </c>
       <c r="AM3">
-        <v>364</v>
+        <v>6756</v>
       </c>
       <c r="AN3">
-        <v>3.653021978021978</v>
+        <v>0.3527603297023668</v>
       </c>
       <c r="AO3">
-        <v>9.62912087912088</v>
+        <v>5.55728241563055</v>
       </c>
       <c r="AP3">
-        <v>2.121153846153846</v>
+        <v>0.1760886273886194</v>
       </c>
       <c r="AQ3">
-        <v>9.62912087912088</v>
+        <v>5.55728241563055</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>China Taiping Insurance Holdings Company Limited (SEHK:966)</t>
+          <t>Yunfeng Financial Group Limited (SEHK:376)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,121 +856,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.107</v>
-      </c>
-      <c r="E4">
-        <v>0.0452</v>
+        <v>1.34</v>
       </c>
       <c r="G4">
-        <v>0.04822702986417039</v>
+        <v>0.01435521173937315</v>
       </c>
       <c r="H4">
-        <v>0.04822702986417039</v>
+        <v>0.01435521173937315</v>
       </c>
       <c r="I4">
-        <v>0.02285993828937747</v>
+        <v>0.09195310630831804</v>
       </c>
       <c r="J4">
-        <v>0.02285993828937747</v>
+        <v>0.0840930883103463</v>
       </c>
       <c r="K4">
-        <v>651.1</v>
+        <v>46.4</v>
       </c>
       <c r="L4">
-        <v>0.01658950715583334</v>
+        <v>0.03700454581705079</v>
       </c>
       <c r="M4">
-        <v>183.2</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.04089011896524786</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.2813699892489633</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>183.2</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04089011896524786</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.2813699892489633</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>6426.1</v>
+        <v>387.4</v>
       </c>
       <c r="V4">
-        <v>1.434301274468228</v>
+        <v>0.7824681882447989</v>
       </c>
       <c r="W4">
-        <v>0.05504874151356561</v>
+        <v>0.03449301219149568</v>
       </c>
       <c r="X4">
-        <v>0.2816271256088478</v>
+        <v>0.1125797186908479</v>
       </c>
       <c r="Y4">
-        <v>-0.2265783840952822</v>
+        <v>-0.07808670649935218</v>
       </c>
       <c r="Z4">
-        <v>1.830736722299447</v>
+        <v>0.9028657834101383</v>
       </c>
       <c r="AA4">
-        <v>0.04185052849586253</v>
+        <v>0.07592477205669876</v>
       </c>
       <c r="AB4">
-        <v>0.09908089149093988</v>
+        <v>0.08240411114023963</v>
       </c>
       <c r="AC4">
-        <v>-0.05723036299507735</v>
+        <v>-0.006479339083540869</v>
       </c>
       <c r="AD4">
-        <v>17996.6</v>
+        <v>433.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>17996.6</v>
+        <v>433.2</v>
       </c>
       <c r="AG4">
-        <v>11570.5</v>
+        <v>45.80000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.8006709110242071</v>
+        <v>0.4666594850802542</v>
       </c>
       <c r="AI4">
-        <v>0.5661141816374486</v>
+        <v>0.1718911197524006</v>
       </c>
       <c r="AJ4">
-        <v>0.7208674957011487</v>
+        <v>0.08467369199482346</v>
       </c>
       <c r="AK4">
-        <v>0.4561852418426406</v>
+        <v>0.02147411852963241</v>
       </c>
       <c r="AL4">
-        <v>414.4</v>
+        <v>23.6</v>
       </c>
       <c r="AM4">
-        <v>414.4</v>
+        <v>23.6</v>
       </c>
       <c r="AN4">
-        <v>14.91266158435532</v>
+        <v>3.536326530612245</v>
       </c>
       <c r="AO4">
-        <v>2.165057915057915</v>
+        <v>4.885593220338983</v>
       </c>
       <c r="AP4">
-        <v>9.587752734504473</v>
+        <v>0.3738775510204083</v>
       </c>
       <c r="AQ4">
-        <v>2.165057915057915</v>
+        <v>4.885593220338983</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yunfeng Financial Group Limited (SEHK:376)</t>
+          <t>China Taiping Insurance Holdings Company Limited (SEHK:966)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,115 +984,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>1.8</v>
+        <v>0.0697</v>
+      </c>
+      <c r="E5">
+        <v>-0.163</v>
       </c>
       <c r="G5">
-        <v>0.1268539521898447</v>
+        <v>0.02664538501931466</v>
       </c>
       <c r="H5">
-        <v>0.1268539521898447</v>
+        <v>0.02664538501931466</v>
       </c>
       <c r="I5">
-        <v>0.0246030361193509</v>
+        <v>0.0221533630375219</v>
       </c>
       <c r="J5">
-        <v>0.02221697684117867</v>
+        <v>0.0221533630375219</v>
       </c>
       <c r="K5">
-        <v>-18.4</v>
+        <v>470.2</v>
       </c>
       <c r="L5">
-        <v>-0.01605304484383179</v>
+        <v>0.01222308296203098</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>211</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.06824724261733027</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.4487452148022119</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>211</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.06824724261733027</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.4487452148022119</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>397.2</v>
+        <v>7240.1</v>
       </c>
       <c r="V5">
-        <v>0.7413213885778276</v>
+        <v>2.34178607238736</v>
       </c>
       <c r="W5">
-        <v>-0.0103446337212571</v>
+        <v>0.04410343954302008</v>
       </c>
       <c r="X5">
-        <v>0.1328818500431708</v>
+        <v>0.2796618438801273</v>
       </c>
       <c r="Y5">
-        <v>-0.1432264837644279</v>
+        <v>-0.2355584043371072</v>
       </c>
       <c r="Z5">
-        <v>0.6409439132136666</v>
+        <v>1.737505589456141</v>
       </c>
       <c r="AA5">
-        <v>0.01423983607636247</v>
+        <v>0.03849159210294537</v>
       </c>
       <c r="AB5">
-        <v>0.09639699992194666</v>
+        <v>0.08414201284321103</v>
       </c>
       <c r="AC5">
-        <v>-0.08215716384558419</v>
+        <v>-0.04565042074026566</v>
       </c>
       <c r="AD5">
-        <v>440.8</v>
+        <v>17216.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>440.8</v>
+        <v>17216.3</v>
       </c>
       <c r="AG5">
-        <v>43.60000000000002</v>
+        <v>9976.199999999999</v>
       </c>
       <c r="AH5">
-        <v>0.4513618677042802</v>
+        <v>0.8477595036438842</v>
       </c>
       <c r="AI5">
-        <v>0.1819457629917035</v>
+        <v>0.5212495723442198</v>
       </c>
       <c r="AJ5">
-        <v>0.07525025888850539</v>
+        <v>0.7634126370725213</v>
       </c>
       <c r="AK5">
-        <v>0.02152554924709949</v>
+        <v>0.3868423501675146</v>
       </c>
       <c r="AL5">
-        <v>18.3</v>
+        <v>491</v>
       </c>
       <c r="AM5">
-        <v>18.3</v>
+        <v>491</v>
       </c>
       <c r="AN5">
-        <v>8.132841328413283</v>
+        <v>14.95119409465914</v>
       </c>
       <c r="AO5">
-        <v>1.540983606557377</v>
+        <v>1.735641547861507</v>
       </c>
       <c r="AP5">
-        <v>0.8044280442804432</v>
+        <v>8.663656100738166</v>
       </c>
       <c r="AQ5">
-        <v>1.540983606557377</v>
+        <v>1.735641547861507</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.7048500000000001</v>
+        <v>-0.115</v>
       </c>
       <c r="E2">
-        <v>-0.163</v>
+        <v>-0.0363</v>
       </c>
       <c r="F2">
-        <v>2.082</v>
+        <v>0.1685</v>
       </c>
       <c r="G2">
-        <v>0.03246081980099513</v>
+        <v>0.2644914454389399</v>
       </c>
       <c r="H2">
-        <v>0.03246081980099513</v>
+        <v>0.2644914454389399</v>
       </c>
       <c r="I2">
-        <v>0.4041860079488603</v>
+        <v>0.2695610495621898</v>
       </c>
       <c r="J2">
-        <v>0.3631624815321022</v>
+        <v>0.1825348895158149</v>
       </c>
       <c r="K2">
-        <v>1505.6</v>
+        <v>6601</v>
       </c>
       <c r="L2">
-        <v>0.01580116724616174</v>
+        <v>0.1393771629220008</v>
       </c>
       <c r="M2">
-        <v>6800</v>
+        <v>6518.6</v>
       </c>
       <c r="N2">
-        <v>0.0665063992848606</v>
+        <v>0.06235108329579031</v>
       </c>
       <c r="O2">
-        <v>4.516471838469713</v>
+        <v>0.9875170428722921</v>
       </c>
       <c r="P2">
-        <v>2492</v>
+        <v>3071.6</v>
       </c>
       <c r="Q2">
-        <v>0.02437263926733421</v>
+        <v>0.0293801717318672</v>
       </c>
       <c r="R2">
-        <v>1.655154091392136</v>
+        <v>0.4653234358430541</v>
       </c>
       <c r="S2">
-        <v>4308</v>
+        <v>3447</v>
       </c>
       <c r="T2">
-        <v>0.6335294117647059</v>
+        <v>0.5287945264320559</v>
       </c>
       <c r="U2">
-        <v>14293.5</v>
+        <v>20620.2</v>
       </c>
       <c r="V2">
-        <v>0.1397954732614934</v>
+        <v>0.1972343459908347</v>
       </c>
       <c r="W2">
-        <v>0.03449301219149568</v>
+        <v>0.07163300874626245</v>
       </c>
       <c r="X2">
-        <v>0.1125797186908479</v>
+        <v>0.09436895622031795</v>
       </c>
       <c r="Y2">
-        <v>-0.07808670649935218</v>
+        <v>-0.0227359474740555</v>
       </c>
       <c r="Z2">
-        <v>1.351419084994759</v>
+        <v>0.5600455503288563</v>
       </c>
       <c r="AA2">
-        <v>0.07592477205669876</v>
+        <v>0.1091180142347344</v>
       </c>
       <c r="AB2">
-        <v>0.08240411114023963</v>
+        <v>0.08532533898702566</v>
       </c>
       <c r="AC2">
-        <v>-0.006479339083540869</v>
+        <v>0.02381646008610737</v>
       </c>
       <c r="AD2">
-        <v>30959.5</v>
+        <v>36667.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>30959.5</v>
+        <v>36667.3</v>
       </c>
       <c r="AG2">
-        <v>16666</v>
+        <v>16047.1</v>
       </c>
       <c r="AH2">
-        <v>0.2324194307583858</v>
+        <v>0.2596576826660246</v>
       </c>
       <c r="AI2">
-        <v>0.3397099471005134</v>
+        <v>0.3317776247605588</v>
       </c>
       <c r="AJ2">
-        <v>0.1401542992369134</v>
+        <v>0.1330673716227534</v>
       </c>
       <c r="AK2">
-        <v>0.2168877274809478</v>
+        <v>0.1785044077977697</v>
       </c>
       <c r="AL2">
-        <v>7270.6</v>
+        <v>1501.9</v>
       </c>
       <c r="AM2">
-        <v>7270.6</v>
+        <v>1501.9</v>
       </c>
       <c r="AN2">
-        <v>0.7937315728752724</v>
+        <v>2.690644789656362</v>
       </c>
       <c r="AO2">
-        <v>5.297018127802382</v>
+        <v>8.500299620480725</v>
       </c>
       <c r="AP2">
-        <v>0.4272785540315344</v>
+        <v>1.177535460862802</v>
       </c>
       <c r="AQ2">
-        <v>5.297018127802382</v>
+        <v>8.500299620480725</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AIA Group Limited (SEHK:1299)</t>
+          <t>Prudential plc (LSE:PRU)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,119 +724,125 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.306</v>
+      </c>
+      <c r="E3">
+        <v>-0.24</v>
+      </c>
       <c r="F3">
-        <v>2.082</v>
+        <v>0.186</v>
       </c>
       <c r="G3">
-        <v>0.03689572009646881</v>
+        <v>0.382218567251462</v>
       </c>
       <c r="H3">
-        <v>0.03689572009646881</v>
+        <v>0.382218567251462</v>
       </c>
       <c r="I3">
-        <v>0.6757316151326446</v>
+        <v>0.3053728070175439</v>
       </c>
       <c r="J3">
-        <v>0.5277386834534038</v>
+        <v>0.1883961226355792</v>
       </c>
       <c r="K3">
-        <v>989</v>
+        <v>877</v>
       </c>
       <c r="L3">
-        <v>0.01779993520751593</v>
+        <v>0.08013523391812866</v>
       </c>
       <c r="M3">
-        <v>6589</v>
+        <v>622</v>
       </c>
       <c r="N3">
-        <v>0.06678559482662504</v>
+        <v>0.02937453954700871</v>
       </c>
       <c r="O3">
-        <v>6.662285136501517</v>
+        <v>0.7092360319270239</v>
       </c>
       <c r="P3">
-        <v>2281</v>
+        <v>562</v>
       </c>
       <c r="Q3">
-        <v>0.02312003973281708</v>
+        <v>0.02654098267752234</v>
       </c>
       <c r="R3">
-        <v>2.306370070778564</v>
+        <v>0.6408209806157354</v>
       </c>
       <c r="S3">
-        <v>4308</v>
+        <v>60</v>
       </c>
       <c r="T3">
-        <v>0.653816967673395</v>
+        <v>0.09646302250803858</v>
       </c>
       <c r="U3">
-        <v>6666</v>
+        <v>5978</v>
       </c>
       <c r="V3">
-        <v>0.06756606087635188</v>
+        <v>0.2823167160964921</v>
       </c>
       <c r="W3">
-        <v>0.0241219512195122</v>
+        <v>0.05111020455737514</v>
       </c>
       <c r="X3">
-        <v>0.08623485124113092</v>
+        <v>0.09436895622031795</v>
       </c>
       <c r="Y3">
-        <v>-0.06211290002161873</v>
+        <v>-0.04325875166294281</v>
       </c>
       <c r="Z3">
-        <v>1.18272382817489</v>
+        <v>0.6958290946083419</v>
       </c>
       <c r="AA3">
-        <v>0.6241691159699865</v>
+        <v>0.1310915034412372</v>
       </c>
       <c r="AB3">
-        <v>0.08139928650075584</v>
+        <v>0.08532533898702566</v>
       </c>
       <c r="AC3">
-        <v>0.5427698294692307</v>
+        <v>0.0457661644542115</v>
       </c>
       <c r="AD3">
-        <v>13310</v>
+        <v>5467</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13310</v>
+        <v>5467</v>
       </c>
       <c r="AG3">
-        <v>6644</v>
+        <v>-511</v>
       </c>
       <c r="AH3">
-        <v>0.1188721878377051</v>
+        <v>0.2052038525925426</v>
       </c>
       <c r="AI3">
-        <v>0.2394487820674271</v>
+        <v>0.2408051799321675</v>
       </c>
       <c r="AJ3">
-        <v>0.06309411887600543</v>
+        <v>-0.02472923663604952</v>
       </c>
       <c r="AK3">
-        <v>0.1358135731807032</v>
+        <v>-0.03055306427503737</v>
       </c>
       <c r="AL3">
-        <v>6756</v>
+        <v>463</v>
       </c>
       <c r="AM3">
-        <v>6756</v>
+        <v>463</v>
       </c>
       <c r="AN3">
-        <v>0.3527603297023668</v>
+        <v>1.453989361702128</v>
       </c>
       <c r="AO3">
-        <v>5.55728241563055</v>
+        <v>7.218142548596112</v>
       </c>
       <c r="AP3">
-        <v>0.1760886273886194</v>
+        <v>-0.1359042553191489</v>
       </c>
       <c r="AQ3">
-        <v>5.55728241563055</v>
+        <v>7.218142548596112</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yunfeng Financial Group Limited (SEHK:376)</t>
+          <t>AIA Group Limited (SEHK:1299)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,115 +862,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>1.34</v>
+        <v>-0.114</v>
+      </c>
+      <c r="E4">
+        <v>0.0357</v>
+      </c>
+      <c r="F4">
+        <v>0.151</v>
       </c>
       <c r="G4">
-        <v>0.01435521173937315</v>
+        <v>0.2819645579268293</v>
       </c>
       <c r="H4">
-        <v>0.01435521173937315</v>
+        <v>0.2819645579268293</v>
       </c>
       <c r="I4">
-        <v>0.09195310630831804</v>
+        <v>0.2882050304878049</v>
       </c>
       <c r="J4">
-        <v>0.0840930883103463</v>
+        <v>0.2414246461095769</v>
       </c>
       <c r="K4">
-        <v>46.4</v>
+        <v>4828</v>
       </c>
       <c r="L4">
-        <v>0.03700454581705079</v>
+        <v>0.2299923780487805</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>5713</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0732480034053334</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>1.183305716652858</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>2326</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02982230980584728</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.4817729908864954</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3387</v>
+      </c>
+      <c r="T4">
+        <v>0.5928583931384561</v>
       </c>
       <c r="U4">
-        <v>387.4</v>
+        <v>8636</v>
       </c>
       <c r="V4">
-        <v>0.7824681882447989</v>
+        <v>0.1107246205861122</v>
       </c>
       <c r="W4">
-        <v>0.03449301219149568</v>
+        <v>0.1155272666363571</v>
       </c>
       <c r="X4">
-        <v>0.1125797186908479</v>
+        <v>0.09230969102128733</v>
       </c>
       <c r="Y4">
-        <v>-0.07808670649935218</v>
+        <v>0.02321757561506978</v>
       </c>
       <c r="Z4">
-        <v>0.9028657834101383</v>
+        <v>0.4519754548390569</v>
       </c>
       <c r="AA4">
-        <v>0.07592477205669876</v>
+        <v>0.1091180142347344</v>
       </c>
       <c r="AB4">
-        <v>0.08240411114023963</v>
+        <v>0.08530155414862702</v>
       </c>
       <c r="AC4">
-        <v>-0.006479339083540869</v>
+        <v>0.02381646008610737</v>
       </c>
       <c r="AD4">
-        <v>433.2</v>
+        <v>15323</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>433.2</v>
+        <v>15323</v>
       </c>
       <c r="AG4">
-        <v>45.80000000000001</v>
+        <v>6687</v>
       </c>
       <c r="AH4">
-        <v>0.4666594850802542</v>
+        <v>0.1642014481618289</v>
       </c>
       <c r="AI4">
-        <v>0.1718911197524006</v>
+        <v>0.2786455965521631</v>
       </c>
       <c r="AJ4">
-        <v>0.08467369199482346</v>
+        <v>0.07896573427977274</v>
       </c>
       <c r="AK4">
-        <v>0.02147411852963241</v>
+        <v>0.144256283033114</v>
       </c>
       <c r="AL4">
-        <v>23.6</v>
+        <v>534</v>
       </c>
       <c r="AM4">
-        <v>23.6</v>
+        <v>534</v>
       </c>
       <c r="AN4">
-        <v>3.536326530612245</v>
+        <v>2.469858156028369</v>
       </c>
       <c r="AO4">
-        <v>4.885593220338983</v>
+        <v>11.32958801498127</v>
       </c>
       <c r="AP4">
-        <v>0.3738775510204083</v>
+        <v>1.077852998065764</v>
       </c>
       <c r="AQ4">
-        <v>4.885593220338983</v>
+        <v>11.32958801498127</v>
       </c>
     </row>
     <row r="5">
@@ -984,46 +999,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0697</v>
+        <v>-0.115</v>
       </c>
       <c r="E5">
-        <v>-0.163</v>
+        <v>-0.0363</v>
       </c>
       <c r="G5">
-        <v>0.02664538501931466</v>
+        <v>0.1571829597982457</v>
       </c>
       <c r="H5">
-        <v>0.02664538501931466</v>
+        <v>0.1571829597982457</v>
       </c>
       <c r="I5">
-        <v>0.0221533630375219</v>
+        <v>0.2187789713900432</v>
       </c>
       <c r="J5">
-        <v>0.0221533630375219</v>
+        <v>0.1262018417798852</v>
       </c>
       <c r="K5">
-        <v>470.2</v>
+        <v>896</v>
       </c>
       <c r="L5">
-        <v>0.01222308296203098</v>
+        <v>0.05808865002236672</v>
       </c>
       <c r="M5">
-        <v>211</v>
+        <v>183.6</v>
       </c>
       <c r="N5">
-        <v>0.06824724261733027</v>
+        <v>0.03414797455641111</v>
       </c>
       <c r="O5">
-        <v>0.4487452148022119</v>
+        <v>0.2049107142857143</v>
       </c>
       <c r="P5">
-        <v>211</v>
+        <v>183.6</v>
       </c>
       <c r="Q5">
-        <v>0.06824724261733027</v>
+        <v>0.03414797455641111</v>
       </c>
       <c r="R5">
-        <v>0.4487452148022119</v>
+        <v>0.2049107142857143</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1032,73 +1047,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>7240.1</v>
+        <v>6006.2</v>
       </c>
       <c r="V5">
-        <v>2.34178607238736</v>
+        <v>1.11710002603876</v>
       </c>
       <c r="W5">
-        <v>0.04410343954302008</v>
+        <v>0.07163300874626245</v>
       </c>
       <c r="X5">
-        <v>0.2796618438801273</v>
+        <v>0.1842763480879696</v>
       </c>
       <c r="Y5">
-        <v>-0.2355584043371072</v>
+        <v>-0.1126433393417072</v>
       </c>
       <c r="Z5">
-        <v>1.737505589456141</v>
+        <v>0.6888240863134578</v>
       </c>
       <c r="AA5">
-        <v>0.03849159210294537</v>
+        <v>0.086930868355105</v>
       </c>
       <c r="AB5">
-        <v>0.08414201284321103</v>
+        <v>0.08550010797309585</v>
       </c>
       <c r="AC5">
-        <v>-0.04565042074026566</v>
+        <v>0.00143076038200915</v>
       </c>
       <c r="AD5">
-        <v>17216.3</v>
+        <v>15877.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>17216.3</v>
+        <v>15877.3</v>
       </c>
       <c r="AG5">
-        <v>9976.199999999999</v>
+        <v>9871.099999999999</v>
       </c>
       <c r="AH5">
-        <v>0.8477595036438842</v>
+        <v>0.7470299568549771</v>
       </c>
       <c r="AI5">
-        <v>0.5212495723442198</v>
+        <v>0.4837145111611427</v>
       </c>
       <c r="AJ5">
-        <v>0.7634126370725213</v>
+        <v>0.6473828839759439</v>
       </c>
       <c r="AK5">
-        <v>0.3868423501675146</v>
+        <v>0.3680842733289829</v>
       </c>
       <c r="AL5">
-        <v>491</v>
+        <v>504.9</v>
       </c>
       <c r="AM5">
-        <v>491</v>
+        <v>504.9</v>
       </c>
       <c r="AN5">
-        <v>14.95119409465914</v>
+        <v>4.333679067609247</v>
       </c>
       <c r="AO5">
-        <v>1.735641547861507</v>
+        <v>6.683699742523272</v>
       </c>
       <c r="AP5">
-        <v>8.663656100738166</v>
+        <v>2.694298113928542</v>
       </c>
       <c r="AQ5">
-        <v>1.735641547861507</v>
+        <v>6.683699742523272</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.115</v>
+        <v>-0.1145</v>
       </c>
       <c r="E2">
-        <v>-0.0363</v>
+        <v>-0.0003000000000000017</v>
       </c>
       <c r="F2">
         <v>0.1685</v>
       </c>
       <c r="G2">
-        <v>0.2644914454389399</v>
+        <v>0.23711621677313</v>
       </c>
       <c r="H2">
-        <v>0.2644914454389399</v>
+        <v>0.23711621677313</v>
       </c>
       <c r="I2">
-        <v>0.2695610495621898</v>
+        <v>0.2432292739885981</v>
       </c>
       <c r="J2">
-        <v>0.1825348895158149</v>
+        <v>0.1680352448490655</v>
       </c>
       <c r="K2">
-        <v>6601</v>
+        <v>7208.4</v>
       </c>
       <c r="L2">
-        <v>0.1393771629220008</v>
+        <v>0.1237791057078096</v>
       </c>
       <c r="M2">
-        <v>6518.6</v>
+        <v>6797.3</v>
       </c>
       <c r="N2">
-        <v>0.06235108329579031</v>
+        <v>0.06229939417269286</v>
       </c>
       <c r="O2">
-        <v>0.9875170428722921</v>
+        <v>0.9429693135786028</v>
       </c>
       <c r="P2">
-        <v>3071.6</v>
+        <v>3350.3</v>
       </c>
       <c r="Q2">
-        <v>0.0293801717318672</v>
+        <v>0.03070655411660114</v>
       </c>
       <c r="R2">
-        <v>0.4653234358430541</v>
+        <v>0.4647772043726764</v>
       </c>
       <c r="S2">
         <v>3447</v>
       </c>
       <c r="T2">
-        <v>0.5287945264320559</v>
+        <v>0.5071131184440881</v>
       </c>
       <c r="U2">
-        <v>20620.2</v>
+        <v>22889.3</v>
       </c>
       <c r="V2">
-        <v>0.1972343459908347</v>
+        <v>0.209787639656484</v>
       </c>
       <c r="W2">
-        <v>0.07163300874626245</v>
+        <v>0.06090857606076422</v>
       </c>
       <c r="X2">
-        <v>0.09436895622031795</v>
+        <v>0.1123614332051004</v>
       </c>
       <c r="Y2">
-        <v>-0.0227359474740555</v>
+        <v>-0.05145285714433623</v>
       </c>
       <c r="Z2">
-        <v>0.5600455503288563</v>
+        <v>0.5885741660451043</v>
       </c>
       <c r="AA2">
-        <v>0.1091180142347344</v>
+        <v>0.09114249194565065</v>
       </c>
       <c r="AB2">
-        <v>0.08532533898702566</v>
+        <v>0.08528340019935118</v>
       </c>
       <c r="AC2">
-        <v>0.02381646008610737</v>
+        <v>0.00596393709968078</v>
       </c>
       <c r="AD2">
-        <v>36667.3</v>
+        <v>42941.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>36667.3</v>
+        <v>42941.2</v>
       </c>
       <c r="AG2">
-        <v>16047.1</v>
+        <v>20051.9</v>
       </c>
       <c r="AH2">
-        <v>0.2596576826660246</v>
+        <v>0.2824183383953246</v>
       </c>
       <c r="AI2">
-        <v>0.3317776247605588</v>
+        <v>0.3371875076069229</v>
       </c>
       <c r="AJ2">
-        <v>0.1330673716227534</v>
+        <v>0.1552498511523402</v>
       </c>
       <c r="AK2">
-        <v>0.1785044077977697</v>
+        <v>0.1919543794956625</v>
       </c>
       <c r="AL2">
-        <v>1501.9</v>
+        <v>1711.4</v>
       </c>
       <c r="AM2">
-        <v>1501.9</v>
+        <v>1711.4</v>
       </c>
       <c r="AN2">
-        <v>2.690644789656362</v>
+        <v>2.823332938840454</v>
       </c>
       <c r="AO2">
-        <v>8.500299620480725</v>
+        <v>8.276674068014492</v>
       </c>
       <c r="AP2">
-        <v>1.177535460862802</v>
+        <v>1.318388628085263</v>
       </c>
       <c r="AQ2">
-        <v>8.500299620480725</v>
+        <v>8.276674068014492</v>
       </c>
     </row>
     <row r="3">
@@ -785,10 +785,10 @@
         <v>0.05111020455737514</v>
       </c>
       <c r="X3">
-        <v>0.09436895622031795</v>
+        <v>0.09434627403892445</v>
       </c>
       <c r="Y3">
-        <v>-0.04325875166294281</v>
+        <v>-0.04323606948154932</v>
       </c>
       <c r="Z3">
         <v>0.6958290946083419</v>
@@ -797,10 +797,10 @@
         <v>0.1310915034412372</v>
       </c>
       <c r="AB3">
-        <v>0.08532533898702566</v>
+        <v>0.08530731127663931</v>
       </c>
       <c r="AC3">
-        <v>0.0457661644542115</v>
+        <v>0.04578419216459785</v>
       </c>
       <c r="AD3">
         <v>5467</v>
@@ -922,10 +922,10 @@
         <v>0.1155272666363571</v>
       </c>
       <c r="X4">
-        <v>0.09230969102128733</v>
+        <v>0.09228797053704396</v>
       </c>
       <c r="Y4">
-        <v>0.02321757561506978</v>
+        <v>0.02323929609931315</v>
       </c>
       <c r="Z4">
         <v>0.4519754548390569</v>
@@ -934,10 +934,10 @@
         <v>0.1091180142347344</v>
       </c>
       <c r="AB4">
-        <v>0.08530155414862702</v>
+        <v>0.08528340019935118</v>
       </c>
       <c r="AC4">
-        <v>0.02381646008610737</v>
+        <v>0.0238346140353832</v>
       </c>
       <c r="AD4">
         <v>15323</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>China Taiping Insurance Holdings Company Limited (SEHK:966)</t>
+          <t>Yunfeng Financial Group Limited (SEHK:376)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -999,121 +999,380 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.115</v>
+        <v>-0.0401</v>
       </c>
       <c r="E5">
-        <v>-0.0363</v>
+        <v>0.392</v>
       </c>
       <c r="G5">
-        <v>0.1571829597982457</v>
+        <v>0.3051724137931034</v>
       </c>
       <c r="H5">
-        <v>0.1571829597982457</v>
+        <v>0.3051724137931034</v>
       </c>
       <c r="I5">
-        <v>0.2187789713900432</v>
+        <v>0.3196120689655172</v>
       </c>
       <c r="J5">
-        <v>0.1262018417798852</v>
+        <v>0.2852131428988895</v>
       </c>
       <c r="K5">
-        <v>896</v>
+        <v>58.9</v>
       </c>
       <c r="L5">
-        <v>0.05808865002236672</v>
+        <v>0.1269396551724138</v>
       </c>
       <c r="M5">
-        <v>183.6</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.03414797455641111</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.2049107142857143</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>183.6</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03414797455641111</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.2049107142857143</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>6006.2</v>
+        <v>581.7</v>
       </c>
       <c r="V5">
-        <v>1.11710002603876</v>
+        <v>1.123189804981657</v>
       </c>
       <c r="W5">
-        <v>0.07163300874626245</v>
+        <v>0.0418859337220879</v>
       </c>
       <c r="X5">
-        <v>0.1842763480879696</v>
+        <v>0.1123614332051004</v>
       </c>
       <c r="Y5">
-        <v>-0.1126433393417072</v>
+        <v>-0.07047549948301254</v>
       </c>
       <c r="Z5">
-        <v>0.6888240863134578</v>
+        <v>0.3195592286501377</v>
       </c>
       <c r="AA5">
-        <v>0.086930868355105</v>
+        <v>0.09114249194565065</v>
       </c>
       <c r="AB5">
-        <v>0.08550010797309585</v>
+        <v>0.08517855484596987</v>
       </c>
       <c r="AC5">
-        <v>0.00143076038200915</v>
+        <v>0.00596393709968078</v>
       </c>
       <c r="AD5">
-        <v>15877.3</v>
+        <v>413.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
+        <v>413.5</v>
+      </c>
+      <c r="AG5">
+        <v>-168.2</v>
+      </c>
+      <c r="AH5">
+        <v>0.4439553360532532</v>
+      </c>
+      <c r="AI5">
+        <v>0.1650962229497724</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.4809837003145556</v>
+      </c>
+      <c r="AK5">
+        <v>-0.08747204742836344</v>
+      </c>
+      <c r="AL5">
+        <v>28.8</v>
+      </c>
+      <c r="AM5">
+        <v>28.8</v>
+      </c>
+      <c r="AN5">
+        <v>2.615433270082227</v>
+      </c>
+      <c r="AO5">
+        <v>5.149305555555556</v>
+      </c>
+      <c r="AP5">
+        <v>-1.063883617963315</v>
+      </c>
+      <c r="AQ5">
+        <v>5.149305555555556</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>China Taiping Insurance Holdings Company Limited (SEHK:966)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.115</v>
+      </c>
+      <c r="E6">
+        <v>-0.0363</v>
+      </c>
+      <c r="G6">
+        <v>0.1571829597982457</v>
+      </c>
+      <c r="H6">
+        <v>0.1571829597982457</v>
+      </c>
+      <c r="I6">
+        <v>0.2187789713900432</v>
+      </c>
+      <c r="J6">
+        <v>0.1262018417798852</v>
+      </c>
+      <c r="K6">
+        <v>896</v>
+      </c>
+      <c r="L6">
+        <v>0.05808865002236672</v>
+      </c>
+      <c r="M6">
+        <v>183.6</v>
+      </c>
+      <c r="N6">
+        <v>0.03414797455641111</v>
+      </c>
+      <c r="O6">
+        <v>0.2049107142857143</v>
+      </c>
+      <c r="P6">
+        <v>183.6</v>
+      </c>
+      <c r="Q6">
+        <v>0.03414797455641111</v>
+      </c>
+      <c r="R6">
+        <v>0.2049107142857143</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>6006.2</v>
+      </c>
+      <c r="V6">
+        <v>1.11710002603876</v>
+      </c>
+      <c r="W6">
+        <v>0.07163300874626245</v>
+      </c>
+      <c r="X6">
+        <v>0.184211678268182</v>
+      </c>
+      <c r="Y6">
+        <v>-0.1125786695219196</v>
+      </c>
+      <c r="Z6">
+        <v>0.6888240863134578</v>
+      </c>
+      <c r="AA6">
+        <v>0.086930868355105</v>
+      </c>
+      <c r="AB6">
+        <v>0.08548374844599399</v>
+      </c>
+      <c r="AC6">
+        <v>0.001447119909111005</v>
+      </c>
+      <c r="AD6">
         <v>15877.3</v>
       </c>
-      <c r="AG5">
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>15877.3</v>
+      </c>
+      <c r="AG6">
         <v>9871.099999999999</v>
       </c>
-      <c r="AH5">
+      <c r="AH6">
         <v>0.7470299568549771</v>
       </c>
-      <c r="AI5">
+      <c r="AI6">
         <v>0.4837145111611427</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ6">
         <v>0.6473828839759439</v>
       </c>
-      <c r="AK5">
+      <c r="AK6">
         <v>0.3680842733289829</v>
       </c>
-      <c r="AL5">
+      <c r="AL6">
         <v>504.9</v>
       </c>
-      <c r="AM5">
+      <c r="AM6">
         <v>504.9</v>
       </c>
-      <c r="AN5">
+      <c r="AN6">
         <v>4.333679067609247</v>
       </c>
-      <c r="AO5">
+      <c r="AO6">
         <v>6.683699742523272</v>
       </c>
-      <c r="AP5">
+      <c r="AP6">
         <v>2.694298113928542</v>
       </c>
-      <c r="AQ5">
+      <c r="AQ6">
         <v>6.683699742523272</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sunshine Insurance Group Company Limited (SEHK:6963)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0.1095540422425634</v>
+      </c>
+      <c r="H7">
+        <v>0.1095540422425634</v>
+      </c>
+      <c r="I7">
+        <v>0.1200426459712044</v>
+      </c>
+      <c r="J7">
+        <v>0.06367244667270087</v>
+      </c>
+      <c r="K7">
+        <v>548.5</v>
+      </c>
+      <c r="L7">
+        <v>0.05268314235494127</v>
+      </c>
+      <c r="M7">
+        <v>278.7</v>
+      </c>
+      <c r="N7">
+        <v>0.06894419156936472</v>
+      </c>
+      <c r="O7">
+        <v>0.5081130355515041</v>
+      </c>
+      <c r="P7">
+        <v>278.7</v>
+      </c>
+      <c r="Q7">
+        <v>0.06894419156936472</v>
+      </c>
+      <c r="R7">
+        <v>0.5081130355515041</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>1687.4</v>
+      </c>
+      <c r="V7">
+        <v>0.4174252919057985</v>
+      </c>
+      <c r="W7">
+        <v>0.06090857606076422</v>
+      </c>
+      <c r="X7">
+        <v>0.1340809071409026</v>
+      </c>
+      <c r="Y7">
+        <v>-0.0731723310801384</v>
+      </c>
+      <c r="Z7">
+        <v>0.8054291991583117</v>
+      </c>
+      <c r="AA7">
+        <v>0.05128364773204376</v>
+      </c>
+      <c r="AB7">
+        <v>0.08499272943488666</v>
+      </c>
+      <c r="AC7">
+        <v>-0.0337090817028429</v>
+      </c>
+      <c r="AD7">
+        <v>5860.4</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>5860.4</v>
+      </c>
+      <c r="AG7">
+        <v>4173</v>
+      </c>
+      <c r="AH7">
+        <v>0.5917922203821142</v>
+      </c>
+      <c r="AI7">
+        <v>0.408994472670426</v>
+      </c>
+      <c r="AJ7">
+        <v>0.5079484869878521</v>
+      </c>
+      <c r="AK7">
+        <v>0.3301058427072951</v>
+      </c>
+      <c r="AL7">
+        <v>180.7</v>
+      </c>
+      <c r="AM7">
+        <v>180.7</v>
+      </c>
+      <c r="AN7">
+        <v>4.116605788142737</v>
+      </c>
+      <c r="AO7">
+        <v>6.916436081903708</v>
+      </c>
+      <c r="AP7">
+        <v>2.931300927226749</v>
+      </c>
+      <c r="AQ7">
+        <v>6.916436081903708</v>
       </c>
     </row>
   </sheetData>
